--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/3ER_TRIMESTRE/FRACCIONES I-X/FRACC X/LTAIPT_A63F10A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/3ER_TRIMESTRE/FRACCIONES I-X/FRACC X/LTAIPT_A63F10A.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\TERCER TRIMESTRE JULIO-SEPTIEMBRE 2024\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885BAD5C-DBAB-480C-9D86-14DE96EBE0DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -22,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="79">
   <si>
     <t>48956</t>
   </si>
@@ -36,7 +42,7 @@
     <t>DESCRIPCIÓN</t>
   </si>
   <si>
-    <t>2021. Plazas vacantes y ocupadas. 2018-2020 Plazas vacantes del personal de base y confianza.</t>
+    <t>Plazas vacantes y ocupadas</t>
   </si>
   <si>
     <t>LTAIPT_A63F10A</t>
@@ -99,9 +105,6 @@
     <t>435852</t>
   </si>
   <si>
-    <t>435846</t>
-  </si>
-  <si>
     <t>435847</t>
   </si>
   <si>
@@ -147,16 +150,28 @@
     <t>Área(s) responsable(s) que genera(n), posee(n), publica(n) y actualizan la información</t>
   </si>
   <si>
-    <t>Fecha de validación</t>
-  </si>
-  <si>
     <t>Fecha de actualización</t>
   </si>
   <si>
     <t>Nota</t>
   </si>
   <si>
-    <t>2023</t>
+    <t>B29E41E3015BA89D14FC0300152E29F8</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>01/07/2024</t>
+  </si>
+  <si>
+    <t>30/09/2024</t>
+  </si>
+  <si>
+    <t>Jefatura de Departamento</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento</t>
   </si>
   <si>
     <t>Directivo</t>
@@ -165,6 +180,9 @@
     <t>Confianza</t>
   </si>
   <si>
+    <t>Departamento de Programación y Presupuesto</t>
+  </si>
+  <si>
     <t>Vacante</t>
   </si>
   <si>
@@ -174,79 +192,55 @@
     <t>Departamento de Recursos Humanos</t>
   </si>
   <si>
-    <t>Jefatura de Departamento</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento</t>
-  </si>
-  <si>
-    <t>Plantel 03 Calpulalpan</t>
-  </si>
-  <si>
-    <t>F2570545BFBEAC01404A8300B9492A7C</t>
-  </si>
-  <si>
-    <t>01/07/2023</t>
-  </si>
-  <si>
-    <t>30/09/2023</t>
+    <t>18/10/2024</t>
+  </si>
+  <si>
+    <t>Durante el período del 01 de julio de 2024 al 30 de septiembre de 2024, en el Colegio de Bachilleres del Estado de Tlaxcala, las plazas vacantes no son concursables  debido a que son plazas directivas. Con fundamento en lo establecido en el articulo 21 fraccion VIII del Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala.  El sexo de las vacantes es indistinto.</t>
+  </si>
+  <si>
+    <t>9425A0B8270B756F819022E96DFB163C</t>
+  </si>
+  <si>
+    <t>Subdirección de área</t>
+  </si>
+  <si>
+    <t>Subdirector de área</t>
+  </si>
+  <si>
+    <t>Subdirección de Servicio Academico</t>
+  </si>
+  <si>
+    <t>31516520040FFF4294EF950275B7C9A4</t>
+  </si>
+  <si>
+    <t>Subdirección de Plantel B</t>
+  </si>
+  <si>
+    <t>Subdirector de Plantel</t>
+  </si>
+  <si>
+    <t>Dirección General</t>
+  </si>
+  <si>
+    <t>D6286E94658A94070CC748AF0216F826</t>
   </si>
   <si>
     <t>Subdirección de Plantel C</t>
   </si>
   <si>
-    <t>Subdirector de Plantel C</t>
-  </si>
-  <si>
-    <t>Plantel 06 Contla</t>
-  </si>
-  <si>
-    <t>13/10/2023</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de julio de 2023 al 30 de septiembre de 2023, en el Colegio de Bachilleres del Estado de Tlaxcala, las plazas vacantes no son concursables  debido a que son plazas directivas.  El sexo de las vacantes es indistinto.</t>
-  </si>
-  <si>
-    <t>FC25C5C3A60D29202FB2C55C644D6ED4</t>
-  </si>
-  <si>
-    <t>54EC189A86D19D65ED4C9EF2DB2EFCC1</t>
-  </si>
-  <si>
-    <t>Subdirección de Servicios Administrativos</t>
-  </si>
-  <si>
-    <t>Subdirector de Área</t>
-  </si>
-  <si>
-    <t>4D62B403497518EF91E6AAB15D5A2EE9</t>
-  </si>
-  <si>
-    <t>Subdirección de Plantel B</t>
-  </si>
-  <si>
-    <t>Subdirector de Plantel B</t>
-  </si>
-  <si>
-    <t>Plantel 09 Tlaxco</t>
-  </si>
-  <si>
-    <t>A1056E66465FF34EDAF68D4A7DF64BB1</t>
-  </si>
-  <si>
-    <t>Departamento de Formación y Desarrollo Docente</t>
-  </si>
-  <si>
-    <t>2AB3068423FDCBD7F063316511400DD9</t>
-  </si>
-  <si>
-    <t>Jefatura de Materia</t>
-  </si>
-  <si>
-    <t>Jefe de Materia</t>
-  </si>
-  <si>
-    <t>Subdirección de Servicio Academico</t>
+    <t>Plantel 02 Huamantla</t>
+  </si>
+  <si>
+    <t>96F89F52EADFAF0AA6B2CD94063E37BF</t>
+  </si>
+  <si>
+    <t>Coordinación de Zona</t>
+  </si>
+  <si>
+    <t>Coordinador de Zona</t>
+  </si>
+  <si>
+    <t>Zona IV</t>
   </si>
   <si>
     <t>Permanente</t>
@@ -276,7 +270,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -372,6 +366,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -387,44 +384,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -452,14 +449,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -487,6 +501,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -498,198 +529,173 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.7109375" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="56.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="43" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="40.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="63.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="58.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="151.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="201.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -706,7 +712,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -721,7 +727,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -759,16 +765,13 @@
         <v>10</v>
       </c>
       <c r="N4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O4" t="s">
-        <v>11</v>
-      </c>
-      <c r="P4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>13</v>
       </c>
@@ -811,13 +814,10 @@
       <c r="O5" t="s">
         <v>26</v>
       </c>
-      <c r="P5" t="s">
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -833,358 +833,289 @@
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-    </row>
-    <row r="7" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:15" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="M7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="N7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="O7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="O7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="N8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="O9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8" s="2" t="s">
+    </row>
+    <row r="10" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K8" s="2" t="s">
+      <c r="E10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="M8" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>63</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="H11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>70</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:P6"/>
+    <mergeCell ref="A6:O6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -1193,13 +1124,13 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H8:H194">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H8:H185" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Hidden_17</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J8:J194">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J8:J185" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>Hidden_29</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K8:K194">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K8:K185" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>Hidden_310</formula1>
     </dataValidation>
   </dataValidations>
@@ -1208,38 +1139,38 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1248,18 +1179,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1268,18 +1199,18 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
